--- a/artfynd/A 32489-2025 artfynd.xlsx
+++ b/artfynd/A 32489-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136356644</v>
       </c>
       <c r="B2" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136356414</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32489-2025 artfynd.xlsx
+++ b/artfynd/A 32489-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136356644</v>
       </c>
       <c r="B2" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136356414</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32489-2025 artfynd.xlsx
+++ b/artfynd/A 32489-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136356644</v>
       </c>
       <c r="B2" t="n">
-        <v>92056</v>
+        <v>92061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136356640</v>
       </c>
       <c r="B3" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136356414</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136356314</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136356325</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136356354</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136356396</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>136356406</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136356711</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136356402</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136356440</v>
       </c>
       <c r="B14" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 32489-2025 artfynd.xlsx
+++ b/artfynd/A 32489-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136356644</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136356414</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32489-2025 artfynd.xlsx
+++ b/artfynd/A 32489-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136356644</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136356640</v>
       </c>
       <c r="B3" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136356414</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136356314</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136356325</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136356354</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136356396</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>136356406</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136356711</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136356440</v>
       </c>
       <c r="B14" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 32489-2025 artfynd.xlsx
+++ b/artfynd/A 32489-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136356644</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136356640</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136356414</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136356314</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136356325</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136356354</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136356396</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>136356406</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136356711</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136356440</v>
       </c>
       <c r="B14" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
